--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibz\source\repos\RestAPI_AutomationFramework\TestData\UploadFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="21585" windowHeight="11385"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="AddMultiMember_Response" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191028"/>
 </workbook>
 </file>
 
@@ -74,7 +75,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>sample2test2member@rovicare.com</t>
+    <t>sample3test3member@rovicare.com</t>
   </si>
   <si>
     <t>CEO</t>
@@ -86,113 +87,277 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>sample1test1member@rovicare.com</t>
+    <t>Member1</t>
+  </si>
+  <si>
+    <t>sample4test4member@rovicare.com</t>
+  </si>
+  <si>
+    <t>Sample2</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>Member2</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>sample5test5member@rovicare.com</t>
+  </si>
+  <si>
+    <t>Team Lead</t>
+  </si>
+  <si>
+    <t>MemberId</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="5">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -341,133 +506,246 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryRight="0" summaryBelow="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="14.42578" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="20.14063" customWidth="1"/>
-    <col min="11" max="11" width="31.14063" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28516" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.14063" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.71094" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85547" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.57031" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.14063" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85547" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.57031" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.42578" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.71094" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>1111111111</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>2222222222</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>3333333333</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>1111111111</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>2222222222</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>3333333333</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="K3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1111112221</v>
+      </c>
+      <c r="G4" s="4">
+        <v>32323333333</v>
+      </c>
+      <c r="H4" s="4">
+        <v>3333333333</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" display="sample2test2member@rovicare.com"/>
-    <hyperlink ref="K3" r:id="rId2" display="sample1test1member@rovicare.com"/>
+    <hyperlink ref="K2" r:id="rId1"/>
+    <hyperlink ref="K3" r:id="rId2"/>
   </hyperlinks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.28516" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.14063" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.57031" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.710938" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28516" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28516" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.57031" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85547" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.14063" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.855469" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.57031" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28516" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.425781" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -119,34 +119,34 @@
     <x:t>Status</x:t>
   </x:si>
   <x:si>
+    <x:t>32323333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111111</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>1111111111</x:t>
+    <x:t>1111112221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Email already registered.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333333</x:t>
   </x:si>
   <x:si>
     <x:t>2222222222</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>Email already registered.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111112221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32323333333</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -745,8 +745,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="K2" r:id="rId6"/>
-    <x:hyperlink ref="K3" r:id="rId7"/>
+    <x:hyperlink ref="K2" r:id="rId10"/>
+    <x:hyperlink ref="K3" r:id="rId11"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -826,7 +826,7 @@
     </x:row>
     <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
@@ -841,13 +841,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>16</x:v>
@@ -865,12 +865,12 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
       <x:c r="A3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>20</x:v>
@@ -885,13 +885,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>16</x:v>
@@ -909,12 +909,12 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>24</x:v>
@@ -929,13 +929,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>16</x:v>
@@ -953,7 +953,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -745,8 +745,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="K2" r:id="rId10"/>
-    <x:hyperlink ref="K3" r:id="rId11"/>
+    <x:hyperlink ref="K2" r:id="rId8"/>
+    <x:hyperlink ref="K3" r:id="rId9"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
+  <x:workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ibz\source\repos\RestAPI_AutomationFramework\TestData\UploadFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="0" activeTab="1"/>
+    <x:workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <x:t>CEO</x:t>
   </x:si>
   <x:si>
-    <x:t>Sample1</x:t>
+    <x:t>Sample23</x:t>
   </x:si>
   <x:si>
     <x:t>Test1</x:t>
@@ -92,13 +92,13 @@
     <x:t>Member1</x:t>
   </x:si>
   <x:si>
-    <x:t>sample4test4member@rovicare.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sample2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Test2</x:t>
+    <x:t>sample44test4member@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sample26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test2r</x:t>
   </x:si>
   <x:si>
     <x:t>Member2</x:t>
@@ -107,10 +107,7 @@
     <x:t>Case Manager</x:t>
   </x:si>
   <x:si>
-    <x:t>sample5test5member@rovicare.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Team Lead</x:t>
+    <x:t>sample55test5member@rovicare.com</x:t>
   </x:si>
   <x:si>
     <x:t>MemberId</x:t>
@@ -122,31 +119,34 @@
     <x:t>32323333333</x:t>
   </x:si>
   <x:si>
+    <x:t>1111112221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222222</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>Email already registered.</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
+    <x:t>User exists in same organization</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333333</x:t>
+  </x:si>
+  <x:si>
     <x:t>1111111111</x:t>
   </x:si>
   <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111112221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Email already registered.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222222</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -230,9 +230,8 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -252,11 +251,11 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -270,9 +269,8 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="2">
+  <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <x:cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </x:cellStyles>
   <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
 </x:styleSheet>
@@ -740,7 +738,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L4" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -761,7 +759,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N4"/>
+  <x:dimension ref="A1:N13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.28516" style="0" bestFit="1" customWidth="1"/>
@@ -774,10 +772,10 @@
     <x:col min="8" max="8" width="14.57031" style="0" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="16.85547" style="0" bestFit="1" customWidth="1"/>
     <x:col min="10" max="10" width="19.14063" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="11" max="11" width="5.855469" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="11" max="11" width="33.71094" style="0" bestFit="1" customWidth="1"/>
     <x:col min="12" max="12" width="11.57031" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="10.28516" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="14" max="14" width="6.425781" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="13" width="10.42578" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="14" max="14" width="23" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:14" s="2" customFormat="1">
@@ -818,15 +816,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="N1" s="2" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
@@ -841,13 +839,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>16</x:v>
@@ -862,15 +860,15 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
       <x:c r="A3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>20</x:v>
@@ -885,13 +883,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>16</x:v>
@@ -906,15 +904,15 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>24</x:v>
@@ -929,13 +927,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>16</x:v>
@@ -947,14 +945,17 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14">
+      <x:c r="K13" s="2"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -14,6 +14,7 @@
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <x:sheet name="AddMultiMember_Response" sheetId="2" r:id="rId2"/>
+    <x:sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="191028"/>
@@ -59,13 +60,13 @@
     <x:t>Designation</x:t>
   </x:si>
   <x:si>
-    <x:t>Sample</x:t>
+    <x:t>friend</x:t>
   </x:si>
   <x:si>
     <x:t>Test</x:t>
   </x:si>
   <x:si>
-    <x:t>Member</x:t>
+    <x:t>LN</x:t>
   </x:si>
   <x:si>
     <x:t>Organization Admin</x:t>
@@ -77,37 +78,37 @@
     <x:t>No</x:t>
   </x:si>
   <x:si>
-    <x:t>sample3test3member@rovicare.com</x:t>
+    <x:t>LN1@rovicare.com</x:t>
   </x:si>
   <x:si>
     <x:t>CEO</x:t>
   </x:si>
   <x:si>
-    <x:t>Sample23</x:t>
+    <x:t>friend23</x:t>
   </x:si>
   <x:si>
     <x:t>Test1</x:t>
   </x:si>
   <x:si>
-    <x:t>Member1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sample44test4member@rovicare.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sample26</x:t>
+    <x:t>LN1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN2@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>friend26</x:t>
   </x:si>
   <x:si>
     <x:t>Test2r</x:t>
   </x:si>
   <x:si>
-    <x:t>Member2</x:t>
+    <x:t>LN2</x:t>
   </x:si>
   <x:si>
     <x:t>Case Manager</x:t>
   </x:si>
   <x:si>
-    <x:t>sample55test5member@rovicare.com</x:t>
+    <x:t>LN3@rovicare.com</x:t>
   </x:si>
   <x:si>
     <x:t>MemberId</x:t>
@@ -125,16 +126,13 @@
     <x:t>2222222222</x:t>
   </x:si>
   <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
     <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Email already registered.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
   </x:si>
   <x:si>
     <x:t>User exists in same organization</x:t>
@@ -156,7 +154,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -183,13 +181,6 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:charset val="1"/>
-    </x:font>
-    <x:font>
-      <x:u/>
-      <x:sz val="11"/>
-      <x:color theme="10"/>
-      <x:name val="Calibri"/>
-      <x:scheme val="minor"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
@@ -230,7 +221,7 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -238,14 +229,11 @@
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -255,16 +243,12 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -658,7 +642,7 @@
       <x:c r="J2" s="7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K2" s="8" t="s">
+      <x:c r="K2" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="L2" s="7" t="s">
@@ -696,7 +680,7 @@
       <x:c r="J3" s="7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="K3" s="8" t="s">
+      <x:c r="K3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L3" s="7" t="s">
@@ -742,10 +726,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:hyperlinks>
-    <x:hyperlink ref="K2" r:id="rId8"/>
-    <x:hyperlink ref="K3" r:id="rId9"/>
-  </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -822,138 +802,6 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:14">
-      <x:c r="A2" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14">
-      <x:c r="A3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:14">
-      <x:c r="A4" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="K13" s="2"/>
     </x:row>
@@ -964,4 +812,197 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:N4"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:14">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M1" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N1" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14">
+      <x:c r="A2" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14">
+      <x:c r="A3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14">
+      <x:c r="A4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -120,31 +120,31 @@
     <x:t>32323333333</x:t>
   </x:si>
   <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>1111112221</x:t>
   </x:si>
   <x:si>
+    <x:t>User exists in same organization</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333333</x:t>
+  </x:si>
+  <x:si>
     <x:t>2222222222</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>User exists in same organization</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -868,7 +868,7 @@
     </x:row>
     <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
@@ -883,13 +883,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>16</x:v>
@@ -904,7 +904,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
         <x:v>36</x:v>
@@ -912,7 +912,7 @@
     </x:row>
     <x:row r="3" spans="1:14">
       <x:c r="A3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>20</x:v>
@@ -927,13 +927,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>16</x:v>
@@ -948,7 +948,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
         <x:v>36</x:v>
@@ -956,7 +956,7 @@
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>24</x:v>
@@ -971,13 +971,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>16</x:v>
@@ -992,7 +992,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
         <x:v>36</x:v>

--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -12,8 +12,8 @@
     <x:workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="AddMultiMember_Response" sheetId="2" r:id="rId2"/>
+    <x:sheet name="Member_Request_UserAlreadyExist" sheetId="1" r:id="rId1"/>
+    <x:sheet name="Member_Respons_UserAlreadyExist" sheetId="2" r:id="rId2"/>
     <x:sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </x:sheets>
   <x:definedNames/>
@@ -108,43 +108,265 @@
     <x:t>Case Manager</x:t>
   </x:si>
   <x:si>
+    <x:t>Test2</x:t>
+  </x:si>
+  <x:si>
     <x:t>LN3@rovicare.com</x:t>
   </x:si>
   <x:si>
+    <x:t>friend30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN4@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manager</x:t>
+  </x:si>
+  <x:si>
+    <x:t>friend31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Care Coordinator</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN5@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>friend32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN6@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Director</x:t>
+  </x:si>
+  <x:si>
+    <x:t>friend33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN7@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>friend34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN8@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Supervisor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>friend35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN9@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>friend36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LN10@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Status</x:t>
+  </x:si>
+  <x:si>
     <x:t>MemberId</x:t>
   </x:si>
   <x:si>
-    <x:t>Status</x:t>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User exists in same organization</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111112221</x:t>
   </x:si>
   <x:si>
     <x:t>32323333333</x:t>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>1111112221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>User exists in same organization</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222222</x:t>
+    <x:t>kaustub.kundet@interbizconsulting.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Email already registered.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333334</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designation not found</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The specified role is not valid.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222229</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222231</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333342</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -204,7 +426,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -220,8 +442,19 @@
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -229,11 +462,20 @@
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -243,12 +485,18 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -556,7 +804,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L4"/>
+  <x:dimension ref="A1:L14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.42578" style="0" bestFit="1" customWidth="1"/>
@@ -574,154 +822,534 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:12" s="1" customFormat="1">
-      <x:c r="A1" s="6" t="s">
+      <x:c r="A1" s="8" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="s">
+      <x:c r="B1" s="8" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="s">
+      <x:c r="C1" s="8" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="s">
+      <x:c r="D1" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="s">
+      <x:c r="E1" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="s">
+      <x:c r="F1" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="s">
+      <x:c r="G1" s="8" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="s">
+      <x:c r="H1" s="8" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="s">
+      <x:c r="I1" s="8" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="s">
+      <x:c r="J1" s="8" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="s">
+      <x:c r="K1" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="s">
+      <x:c r="L1" s="8" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12">
-      <x:c r="A2" s="7">
+      <x:c r="A2" s="9">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="7" t="s">
+      <x:c r="B2" s="9" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C2" s="7" t="s">
+      <x:c r="C2" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D2" s="7" t="s">
+      <x:c r="D2" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E2" s="7" t="s">
+      <x:c r="E2" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F2" s="7">
+      <x:c r="F2" s="9">
         <x:v>1111111111</x:v>
       </x:c>
-      <x:c r="G2" s="7">
+      <x:c r="G2" s="9">
         <x:v>2222222222</x:v>
       </x:c>
-      <x:c r="H2" s="7">
+      <x:c r="H2" s="9">
         <x:v>3333333333</x:v>
       </x:c>
-      <x:c r="I2" s="7" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J2" s="7" t="s">
+      <x:c r="I2" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L2" s="7" t="s">
+      <x:c r="L2" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12">
-      <x:c r="A3" s="7">
+      <x:c r="A3" s="9">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="B3" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
+      <x:c r="C3" s="9" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="s">
+      <x:c r="D3" s="9" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="s">
+      <x:c r="E3" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F3" s="7">
+      <x:c r="F3" s="9">
         <x:v>1111111111</x:v>
       </x:c>
-      <x:c r="G3" s="7">
+      <x:c r="G3" s="9">
         <x:v>2222222222</x:v>
       </x:c>
-      <x:c r="H3" s="7">
+      <x:c r="H3" s="9">
         <x:v>3333333333</x:v>
       </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
+      <x:c r="I3" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L3" s="7" t="s">
+      <x:c r="L3" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12">
-      <x:c r="A4" s="7">
+      <x:c r="A4" s="10">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
+      <x:c r="B4" s="10" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="s">
+      <x:c r="C4" s="10" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="s">
+      <x:c r="D4" s="10" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="s">
+      <x:c r="E4" s="10" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F4" s="7">
+      <x:c r="F4" s="10">
         <x:v>1111112221</x:v>
       </x:c>
-      <x:c r="G4" s="7">
+      <x:c r="G4" s="10">
         <x:v>32323333333</x:v>
       </x:c>
-      <x:c r="H4" s="7">
+      <x:c r="H4" s="10">
         <x:v>3333333333</x:v>
       </x:c>
-      <x:c r="I4" s="7" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K4" s="7" t="s">
+      <x:c r="I4" s="10" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L4" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:12">
+      <x:c r="A5" s="9">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F5" s="7">
+        <x:v>1111111111</x:v>
+      </x:c>
+      <x:c r="G5" s="7">
+        <x:v>2222222222</x:v>
+      </x:c>
+      <x:c r="H5" s="7">
+        <x:v>3333333333</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K5" s="7" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L5" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:12">
+      <x:c r="A6" s="9">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F6" s="7">
+        <x:v>1111111112</x:v>
+      </x:c>
+      <x:c r="G6" s="7">
+        <x:v>2222222223</x:v>
+      </x:c>
+      <x:c r="H6" s="7">
+        <x:v>3333333334</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L6" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:12">
+      <x:c r="A7" s="9">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="L4" s="7" t="s">
+      <x:c r="D7" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F7" s="7">
+        <x:v>1111111113</x:v>
+      </x:c>
+      <x:c r="G7" s="7">
+        <x:v>2222222224</x:v>
+      </x:c>
+      <x:c r="H7" s="7">
+        <x:v>3333333335</x:v>
+      </x:c>
+      <x:c r="I7" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L7" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:12">
+      <x:c r="A8" s="9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="7">
+        <x:v>1111111114</x:v>
+      </x:c>
+      <x:c r="G8" s="7">
+        <x:v>2222222225</x:v>
+      </x:c>
+      <x:c r="H8" s="7">
+        <x:v>3333333336</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K8" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:12">
+      <x:c r="A9" s="9">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F9" s="7">
+        <x:v>1111111115</x:v>
+      </x:c>
+      <x:c r="G9" s="7">
+        <x:v>2222222226</x:v>
+      </x:c>
+      <x:c r="H9" s="7">
+        <x:v>3333333337</x:v>
+      </x:c>
+      <x:c r="I9" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="7" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L9" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:12">
+      <x:c r="A10" s="9">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F10" s="7">
+        <x:v>1111111116</x:v>
+      </x:c>
+      <x:c r="G10" s="7">
+        <x:v>2222222227</x:v>
+      </x:c>
+      <x:c r="H10" s="7">
+        <x:v>3333333338</x:v>
+      </x:c>
+      <x:c r="I10" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K10" s="7" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L10" s="7" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:12">
+      <x:c r="A11" s="9">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F11" s="7">
+        <x:v>1111111117</x:v>
+      </x:c>
+      <x:c r="G11" s="7">
+        <x:v>2222222228</x:v>
+      </x:c>
+      <x:c r="H11" s="7">
+        <x:v>3333333339</x:v>
+      </x:c>
+      <x:c r="I11" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="7" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L11" s="7" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:12">
+      <x:c r="A12" s="9">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F12" s="7">
+        <x:v>1111111118</x:v>
+      </x:c>
+      <x:c r="G12" s="7">
+        <x:v>2222222229</x:v>
+      </x:c>
+      <x:c r="H12" s="7">
+        <x:v>3333333340</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L12" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:12">
+      <x:c r="A13" s="9">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F13" s="7">
+        <x:v>1111111119</x:v>
+      </x:c>
+      <x:c r="G13" s="7">
+        <x:v>2222222230</x:v>
+      </x:c>
+      <x:c r="H13" s="7">
+        <x:v>3333333341</x:v>
+      </x:c>
+      <x:c r="I13" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J13" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="7" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L13" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:12">
+      <x:c r="A14" s="9">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F14" s="7">
+        <x:v>1111111120</x:v>
+      </x:c>
+      <x:c r="G14" s="7">
+        <x:v>2222222231</x:v>
+      </x:c>
+      <x:c r="H14" s="7">
+        <x:v>3333333342</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K14" s="7" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L14" s="7" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -739,7 +1367,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N13"/>
+  <x:dimension ref="A1:N14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.28516" style="0" bestFit="1" customWidth="1"/>
@@ -796,14 +1424,583 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="M1" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14">
+      <x:c r="A2" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14">
+      <x:c r="A3" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14">
+      <x:c r="A4" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14">
+      <x:c r="A5" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14">
+      <x:c r="A6" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14">
+      <x:c r="A7" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="L7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14">
+      <x:c r="A8" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14">
+      <x:c r="A9" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14">
+      <x:c r="A10" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14">
+      <x:c r="A11" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14">
+      <x:c r="A12" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" spans="1:14">
-      <x:c r="K13" s="2"/>
+      <x:c r="A13" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="2" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14">
+      <x:c r="A14" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -819,7 +2016,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N4"/>
+  <x:dimension ref="A1:N14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:14">
@@ -860,15 +2057,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="M1" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="N1" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
@@ -883,13 +2080,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>16</x:v>
@@ -904,15 +2101,15 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
       <x:c r="A3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>20</x:v>
@@ -927,13 +2124,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>16</x:v>
@@ -948,15 +2145,15 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>24</x:v>
@@ -971,13 +2168,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>16</x:v>
@@ -986,16 +2183,456 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14">
+      <x:c r="A5" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14">
+      <x:c r="A6" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14">
+      <x:c r="A7" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14">
+      <x:c r="A8" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14">
+      <x:c r="A9" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>36</x:v>
+      <x:c r="F9" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14">
+      <x:c r="A10" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14">
+      <x:c r="A11" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14">
+      <x:c r="A12" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14">
+      <x:c r="A13" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14">
+      <x:c r="A14" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -246,127 +246,127 @@
     <x:t>32323333333</x:t>
   </x:si>
   <x:si>
+    <x:t>Email already registered.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333334</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designation not found</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The specified role is not valid.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222229</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222231</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333342</x:t>
+  </x:si>
+  <x:si>
     <x:t>kaustub.kundet@interbizconsulting.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Email already registered.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111112</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333334</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111113</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222225</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333336</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designation not found</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111115</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222226</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The specified role is not valid.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222227</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222228</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222229</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111119</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333341</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222231</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333342</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1556,7 +1556,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
         <x:v>69</x:v>
@@ -1600,7 +1600,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
         <x:v>69</x:v>
@@ -1608,7 +1608,7 @@
     </x:row>
     <x:row r="6" spans="1:14">
       <x:c r="A6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>20</x:v>
@@ -1623,13 +1623,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>16</x:v>
@@ -1644,7 +1644,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
         <x:v>69</x:v>
@@ -1652,7 +1652,7 @@
     </x:row>
     <x:row r="7" spans="1:14">
       <x:c r="A7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>24</x:v>
@@ -1667,13 +1667,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
+      <x:c r="H7" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>16</x:v>
@@ -1696,7 +1696,7 @@
     </x:row>
     <x:row r="8" spans="1:14">
       <x:c r="A8" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>30</x:v>
@@ -1711,13 +1711,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="H8" s="0" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>17</x:v>
@@ -1732,7 +1732,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>69</x:v>
@@ -1740,7 +1740,7 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>35</x:v>
@@ -1755,13 +1755,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
         <x:v>16</x:v>
@@ -1776,7 +1776,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
         <x:v>69</x:v>
@@ -1784,7 +1784,7 @@
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>40</x:v>
@@ -1799,13 +1799,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G10" s="0" t="s">
+      <x:c r="H10" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>17</x:v>
@@ -1820,7 +1820,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>69</x:v>
@@ -1828,7 +1828,7 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>45</x:v>
@@ -1843,13 +1843,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
+      <x:c r="H11" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>16</x:v>
@@ -1872,7 +1872,7 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>49</x:v>
@@ -1887,13 +1887,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G12" s="0" t="s">
+      <x:c r="H12" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>17</x:v>
@@ -1908,7 +1908,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
         <x:v>69</x:v>
@@ -1916,7 +1916,7 @@
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>54</x:v>
@@ -1931,13 +1931,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G13" s="0" t="s">
+      <x:c r="H13" s="0" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>16</x:v>
@@ -1952,7 +1952,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
         <x:v>69</x:v>
@@ -1960,7 +1960,7 @@
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>58</x:v>
@@ -1975,13 +1975,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G14" s="0" t="s">
+      <x:c r="H14" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
         <x:v>17</x:v>
@@ -2183,7 +2183,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>19</x:v>
@@ -2233,7 +2233,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
         <x:v>69</x:v>
@@ -2241,7 +2241,7 @@
     </x:row>
     <x:row r="6" spans="1:14">
       <x:c r="A6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>20</x:v>
@@ -2256,13 +2256,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>16</x:v>
@@ -2277,7 +2277,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
         <x:v>69</x:v>
@@ -2285,7 +2285,7 @@
     </x:row>
     <x:row r="7" spans="1:14">
       <x:c r="A7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>24</x:v>
@@ -2300,13 +2300,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
+      <x:c r="H7" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>16</x:v>
@@ -2329,7 +2329,7 @@
     </x:row>
     <x:row r="8" spans="1:14">
       <x:c r="A8" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>30</x:v>
@@ -2344,13 +2344,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="H8" s="0" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
         <x:v>17</x:v>
@@ -2365,7 +2365,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>69</x:v>
@@ -2373,7 +2373,7 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>35</x:v>
@@ -2388,13 +2388,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
+      <x:c r="H9" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
         <x:v>16</x:v>
@@ -2409,7 +2409,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
         <x:v>69</x:v>
@@ -2417,7 +2417,7 @@
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>40</x:v>
@@ -2432,13 +2432,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G10" s="0" t="s">
+      <x:c r="H10" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
         <x:v>17</x:v>
@@ -2453,7 +2453,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>69</x:v>
@@ -2461,7 +2461,7 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>45</x:v>
@@ -2476,13 +2476,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G11" s="0" t="s">
+      <x:c r="H11" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
         <x:v>16</x:v>
@@ -2505,7 +2505,7 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>49</x:v>
@@ -2520,13 +2520,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G12" s="0" t="s">
+      <x:c r="H12" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
         <x:v>17</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
         <x:v>69</x:v>
@@ -2549,7 +2549,7 @@
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>54</x:v>
@@ -2564,13 +2564,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G13" s="0" t="s">
+      <x:c r="H13" s="0" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
         <x:v>16</x:v>
@@ -2585,7 +2585,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
         <x:v>69</x:v>
@@ -2593,7 +2593,7 @@
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>58</x:v>
@@ -2608,13 +2608,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G14" s="0" t="s">
+      <x:c r="H14" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="H14" s="0" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
         <x:v>17</x:v>

--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -15,6 +15,7 @@
     <x:sheet name="Member_RequestSheet" sheetId="1" r:id="rId1"/>
     <x:sheet name="Member_ResponseSheet" sheetId="2" r:id="rId2"/>
     <x:sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <x:sheet name="Member_Respons_UserAlreadyExist" sheetId="4" r:id="rId8"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr/>
@@ -321,100 +322,76 @@
     <x:t>MemberId</x:t>
   </x:si>
   <x:si>
-    <x:t>Success! Member information added. MemberId:Success! Member information added. MemberId:818795f7-91ab-4942-b711-c68429907b82, BusinessunitMemberId:1d61e42c-d7e0-4e5d-8b6b-abaa5fd82b8b</x:t>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>User exists in same organization</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111112221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32323333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Email already registered.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The specified role is not valid.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designation not found</x:t>
   </x:si>
   <x:si>
     <x:t>10</x:t>
   </x:si>
   <x:si>
-    <x:t>Designation not found</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111112221</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>12</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success! Member information added. MemberId:390c8df7-0314-4258-b8b8-75684b15bd70, BusinessunitMemberId:aebd38cd-bdf3-4e91-9af3-b00e74443f81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success! Member information added. MemberId:Success! Member information added. MemberId:390c8df7-0314-4258-b8b8-75684b15bd70, BusinessunitMemberId:aebd38cd-bdf3-4e91-9af3-b00e74443f81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The specified role is not valid.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success! Member information added. MemberId:74d1df79-6f01-4c9f-8ae2-2a40aeeed100, BusinessunitMemberId:dbd08d1e-1bd7-4f25-834f-5d053100f1c5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111111111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success! Member information added. MemberId:Success! Member information added. MemberId:74d1df79-6f01-4c9f-8ae2-2a40aeeed100, BusinessunitMemberId:dbd08d1e-1bd7-4f25-834f-5d053100f1c5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3333333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>User exists in same organization</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Email already registered.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32323333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2222222222</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success! Member information added. MemberId:818795f7-91ab-4942-b711-c68429907b82, BusinessunitMemberId:1d61e42c-d7e0-4e5d-8b6b-abaa5fd82b8b</x:t>
-  </x:si>
-  <x:si>
     <x:t>13</x:t>
   </x:si>
   <x:si>
     <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success! Member information added. MemberId:Success! Member information added. MemberId:4c8bbf52-45ef-4b4d-9a48-c2dee726abdb, BusinessunitMemberId:da29664c-f072-4fae-b587-6bf6dc684710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success! Member information added. MemberId:4c8bbf52-45ef-4b4d-9a48-c2dee726abdb, BusinessunitMemberId:da29664c-f072-4fae-b587-6bf6dc684710</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1375,7 +1352,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="K2" r:id="rId7"/>
+    <x:hyperlink ref="K2" r:id="rId9"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -1439,7 +1416,7 @@
     </x:row>
     <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>12</x:v>
@@ -1454,13 +1431,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
         <x:v>16</x:v>
@@ -1475,7 +1452,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
         <x:v>104</x:v>
@@ -1483,7 +1460,7 @@
     </x:row>
     <x:row r="3" spans="1:14">
       <x:c r="A3" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>20</x:v>
@@ -1498,13 +1475,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>16</x:v>
@@ -1519,7 +1496,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
         <x:v>104</x:v>
@@ -1527,7 +1504,7 @@
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>23</x:v>
@@ -1542,13 +1519,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>16</x:v>
@@ -1563,7 +1540,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
         <x:v>104</x:v>
@@ -1571,7 +1548,7 @@
     </x:row>
     <x:row r="5" spans="1:14">
       <x:c r="A5" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>27</x:v>
@@ -1586,13 +1563,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>16</x:v>
@@ -1607,7 +1584,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
         <x:v>104</x:v>
@@ -1615,7 +1592,7 @@
     </x:row>
     <x:row r="6" spans="1:14">
       <x:c r="A6" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>31</x:v>
@@ -1651,7 +1628,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
         <x:v>104</x:v>
@@ -1659,7 +1636,7 @@
     </x:row>
     <x:row r="7" spans="1:14">
       <x:c r="A7" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>38</x:v>
@@ -1695,15 +1672,15 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:14">
       <x:c r="A8" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>45</x:v>
@@ -1739,7 +1716,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>104</x:v>
@@ -1747,7 +1724,7 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>52</x:v>
@@ -1783,15 +1760,15 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>59</x:v>
@@ -1827,7 +1804,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>104</x:v>
@@ -1835,7 +1812,7 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>66</x:v>
@@ -1871,7 +1848,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
         <x:v>104</x:v>
@@ -1879,7 +1856,7 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>72</x:v>
@@ -1915,7 +1892,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
         <x:v>104</x:v>
@@ -1923,7 +1900,7 @@
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>78</x:v>
@@ -1959,15 +1936,15 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>85</x:v>
@@ -2003,7 +1980,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
         <x:v>104</x:v>
@@ -2011,7 +1988,7 @@
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>91</x:v>
@@ -2047,10 +2024,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2076,4 +2053,681 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:N15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:14">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M1" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="N1" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14">
+      <x:c r="A2" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14">
+      <x:c r="A3" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14">
+      <x:c r="A4" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14">
+      <x:c r="A5" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14">
+      <x:c r="A6" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14">
+      <x:c r="A7" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14">
+      <x:c r="A8" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14">
+      <x:c r="A9" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14">
+      <x:c r="A10" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14">
+      <x:c r="A11" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14">
+      <x:c r="A12" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14">
+      <x:c r="A13" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14">
+      <x:c r="A14" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:14">
+      <x:c r="A15" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -334,7 +334,7 @@
     <x:t>3333333333</x:t>
   </x:si>
   <x:si>
-    <x:t>User exists in same organization</x:t>
+    <x:t>Sorry! You already have maximum numbers of members.</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -367,16 +367,10 @@
     <x:t>7</x:t>
   </x:si>
   <x:si>
-    <x:t>The specified role is not valid.</x:t>
-  </x:si>
-  <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designation not found</x:t>
   </x:si>
   <x:si>
     <x:t>10</x:t>
@@ -1716,7 +1710,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>104</x:v>
@@ -1724,7 +1718,7 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>52</x:v>
@@ -1768,7 +1762,7 @@
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>59</x:v>
@@ -1804,7 +1798,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>104</x:v>
@@ -1812,7 +1806,7 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>66</x:v>
@@ -1848,7 +1842,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
         <x:v>104</x:v>
@@ -1856,7 +1850,7 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>72</x:v>
@@ -1900,7 +1894,7 @@
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>78</x:v>
@@ -1944,7 +1938,7 @@
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>85</x:v>
@@ -1980,7 +1974,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
         <x:v>104</x:v>
@@ -1988,7 +1982,7 @@
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>91</x:v>
@@ -2409,7 +2403,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>104</x:v>
@@ -2417,7 +2411,7 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>52</x:v>
@@ -2461,7 +2455,7 @@
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>59</x:v>
@@ -2497,7 +2491,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>104</x:v>
@@ -2505,7 +2499,7 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>66</x:v>
@@ -2541,7 +2535,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
         <x:v>104</x:v>
@@ -2549,7 +2543,7 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>72</x:v>
@@ -2593,7 +2587,7 @@
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>78</x:v>
@@ -2637,7 +2631,7 @@
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>85</x:v>
@@ -2673,7 +2667,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
         <x:v>104</x:v>
@@ -2681,7 +2675,7 @@
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>91</x:v>
